--- a/docs/referral-pricing/ロイ様ご紹介プラン_価格表.xlsx
+++ b/docs/referral-pricing/ロイ様ご紹介プラン_価格表.xlsx
@@ -389,7 +389,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="173">
   <si>
     <t xml:space="preserve">ロイ様ご紹介プラン｜補綴（セラミック治療）価格表　※医院内部用・粗利つき</t>
   </si>
@@ -1544,7 +1544,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">単位：円 ／ 矯正は【定価据え置き・値引きなし】＋【矯正検査診断料 </t>
+      <t xml:space="preserve">単位：円 ／ 矯正は【①矯正治療費】と【②矯正検査診断料】の別建て請求。紹介特典は②のみ無料にするもので、①のパッケージ価格は</t>
     </r>
     <r>
       <rPr>
@@ -1554,7 +1554,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">44,000</t>
+      <t xml:space="preserve">1</t>
     </r>
     <r>
       <rPr>
@@ -1563,29 +1563,29 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">円を無料】が紹介特典。パッケージ価格そのものは</t>
-    </r>
+      <t xml:space="preserve">円も下げない。</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="9"/>
         <color rgb="FF666666"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">根拠：元データ 矯正</t>
     </r>
     <r>
       <rPr>
         <sz val="9"/>
         <color rgb="FF666666"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">円も下げない。</t>
-    </r>
-  </si>
-  <si>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_</t>
+    </r>
     <r>
       <rPr>
         <sz val="9"/>
@@ -1593,7 +1593,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">根拠：元データ 矯正</t>
+      <t xml:space="preserve">値引き価格表 </t>
     </r>
     <r>
       <rPr>
@@ -1603,7 +1603,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_</t>
+      <t xml:space="preserve">A25</t>
     </r>
     <r>
       <rPr>
@@ -1612,7 +1612,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">値引き価格表 </t>
+      <t xml:space="preserve">「値引きを求められた場合は、価格を下げるより矯正検査診断料</t>
     </r>
     <r>
       <rPr>
@@ -1622,7 +1622,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">A25</t>
+      <t xml:space="preserve">44,000</t>
     </r>
     <r>
       <rPr>
@@ -1631,36 +1631,1640 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">「値引きを求められた場合は、価格を下げるより矯正検査診断料</t>
-    </r>
+      <t xml:space="preserve">円（原価ゼロ）を無料にするほうが医院の負担が小さい」</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">【設定値】（青字＝入力セル）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">無料にする矯正検査診断料（税込・アラインへの支払いなし＝丸ごと利益）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">［比較用］どうしても値引きする場合の下限割引率</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">①矯正治療費
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">税込・据え置き</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">パッケージ
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">22%OFF</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">後</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">手数料
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">割引なし</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ビベラ</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1set
+(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">割引なし</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">原価合計</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">通常時の請求額
+①</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+②</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">ロイ紹介の請求額
+①のみ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">②矯正検査診断料
+→無料にする額</t>
+  </si>
+  <si>
+    <t xml:space="preserve">請求総額に対する
+実質割引率</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">［比較］治療費を</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10%OFF
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">にした場合の値引額</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">■ 大人（インビザライン）　※アライン価格は税別・</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">22%OFF</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">適用</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">インビザラインフル（無制限）｜コンプリ オプション</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">インビザラインフル（無制限）｜コンプリ オプション</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">インビザラインモデレート（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">26</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">枚）両顎</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">インビザラインモデレート 上下別（片顎）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">インビザラインライト（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">14</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">枚）両顎</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">インビザラインライト 上下別（片顎）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">インビザラインエクスプレス（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">枚）両顎</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">インビザラインエクスプレス 上下別（片顎）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">■ 小児一期（インビザライン・ファースト）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">小児一期｜ファースト オプション</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">か月）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">小児一期｜ファースト オプション</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">18</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">か月）★推奨</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">小児一期｜ファースト オプション</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">24</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">か月）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">■ 小児二期</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">小児二期治療（フェーズ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">なぜ矯正は値引かず「検査診断料 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">44,000</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">円 無料」にするのか</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">◆ 矯正の粗利率は定価でも</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">64</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">76%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">と低く、補綴のように</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">20%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">も下げる余地がない。パッケージ価格を下げると原価率が一気に悪化する。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">◆ 検査診断料</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">44,000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">円はアラインへの支払いがゼロ＝丸ごと利益。無料にしても医院の持ち出しは一切発生せず、減るのは「もらえたはずの</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">44,000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">円」だけ。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">◆ M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">列（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10%OFF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の値引額）と </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">I</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">列（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">44,000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">円）を比べると、モデレート以上の高額パッケージでは検査診断料無料のほうが医院の負担が小さい。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">◆【要注意】ライト両顎</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC00000"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(43,780)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・ライト片顎</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC00000"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(39,380)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・エクスプレス両顎</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC00000"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(32,780)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・エクスプレス片顎</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC00000"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(29,800)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">は、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC00000"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10%OFF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">のほうが</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC00000"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">44,000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">円より安く済む（フェーズ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC00000"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">は</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC00000"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">44,000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">円で同額）。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">　　ただし表を</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC00000"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">本立てにすると現場が混乱し「じゃあ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC00000"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10%OFF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">で」と言われる口実にもなるため、全パッケージ一律「検査診断料無料」で統一する。差額は最大</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC00000"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">14,200</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">円（エクスプレス片顎）。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">運用上の注意（元データより引き継ぎ）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">◆ 矯正の請求は【①矯正治療費】と【②矯正検査診断料 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">44,000</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">円】の別建て。②はアラインへの支払いが無いので原価ゼロ＝丸ごと利益。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">◆ 原価合計＝パッケージ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(22%OFF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">後</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＋手数料</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3,400</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（初回アライナー＋ビベラの</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">回分）＋ビベラ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">セット（定価・割引対象外）。②に対応する原価は無い。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">◆ 追加アライナーが出るたびに手数料</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+1,700</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">円、コンプリ オプション</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・モデレート・ライト・フェーズ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">は追加</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">回ごとに本体費用も発生する（元データ参照）。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">◆ エクスプレスはアラインの割引が一切効かない（片顎</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">78,000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／両顎</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">100,000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">が丸ごと請求）。粗利率が最も低いので、紹介プランでも値引きはしない。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">◆ iTero</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">送信の症例はキャンセル料</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">円（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PVS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">印象は</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">30,000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">円）。ロイ様紹介の症例は必ず</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">iTero</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">で提出する運用にすると、キャンセル時の損失をゼロにできる。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">◆ ロイ様から矯正の値引きを強く求められた場合の最終ラインは</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC00000"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">列（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC00000"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10%OFF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）。ただし院長判断とし、価格表には載せない。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">従来の「月額紹介料」と、新方式「紹介の方への値引き」の損益比較</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="9"/>
         <color rgb="FF666666"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">44,000</t>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">この制度の最大のメリットは、紹介料が固定費から変動費に変わること。紹介がゼロの月の医院負担は、従来＝月額まるごと／新方式＝</t>
     </r>
     <r>
       <rPr>
         <sz val="9"/>
         <color rgb="FF666666"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">円（原価ゼロ）を無料にするほうが医院の負担が小さい」</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">【設定値】（青字＝入力セル）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">無料にする矯正検査診断料（税込・アラインへの支払いなし＝丸ごと利益）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">［比較用］どうしても値引きする場合の下限割引率</t>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">円。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">単位：円。補綴の「通常割引率」は既存の本数ルール（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">本</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">本</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">15%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">本以上</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">20%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）を自動適用。矯正は原則値引きなしのため通常割引率</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">【設定値】従来ロイ様に毎月お支払いしていた紹介料の実額を入れてください（青字＝入力セル）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">従来の月額紹介料（実額に置き換えてください）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">円／月　★仮の数値です。必ず実額に修正してください</t>
+  </si>
+  <si>
+    <t xml:space="preserve">従来方式の年間負担</t>
+  </si>
+  <si>
+    <t xml:space="preserve">円／年（紹介人数がゼロでも発生）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">想定ケース</t>
+  </si>
+  <si>
+    <t xml:space="preserve">本数／件数</t>
   </si>
   <si>
     <r>
@@ -1671,8 +3275,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">パッケージ定価
-</t>
+      <t xml:space="preserve">単価</t>
     </r>
     <r>
       <rPr>
@@ -1693,7 +3296,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">税込</t>
+      <t xml:space="preserve">定価</t>
     </r>
     <r>
       <rPr>
@@ -1708,201 +3311,18 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">パッケージ
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">22%OFF</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">後</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">手数料
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">割引なし</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">ビベラ</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1set
-(</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">割引なし</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">原価合計</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">通常の患者総額
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">定価</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">検査診断料</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">ロイ紹介の
-患者総額</t>
+    <t xml:space="preserve">定価合計</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通常の
+割引率</t>
+  </si>
+  <si>
+    <t xml:space="preserve">紹介がなくても
+出していた価格</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ロイ紹介価格</t>
   </si>
   <si>
     <r>
@@ -1935,1498 +3355,6 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">検査診断料</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">総額に対する
-実質割引率</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">［比較］</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">10%OFF</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">にした
-場合の値引額</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">■ 大人（インビザライン）　※アライン価格は税別・</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">22%OFF</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">適用</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">インビザラインフル（無制限）｜コンプリ オプション</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">インビザラインフル（無制限）｜コンプリ オプション</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">インビザラインモデレート（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">26</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">枚）両顎</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">インビザラインモデレート 上下別（片顎）</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">インビザラインライト（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">14</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">枚）両顎</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">インビザラインライト 上下別（片顎）</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">インビザラインエクスプレス（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">7</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">枚）両顎</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">インビザラインエクスプレス 上下別（片顎）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">■ 小児一期（インビザライン・ファースト）</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">小児一期｜ファースト オプション</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">12</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">か月）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">小児一期｜ファースト オプション</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">18</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">か月）★推奨</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">小児一期｜ファースト オプション</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">24</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">か月）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">■ 小児二期</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">小児二期治療（フェーズ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">なぜ矯正は値引かず「検査診断料 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">44,000</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">円 無料」にするのか</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">◆ 矯正の粗利率は定価でも</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">64</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">〜</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">76%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">と低く、補綴のように</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">20%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">も下げる余地がない。パッケージ価格を下げると原価率が一気に悪化する。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">◆ 検査診断料</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">44,000</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">円はアラインへの支払いがゼロ＝丸ごと利益。無料にしても医院の持ち出しは一切発生せず、減るのは「もらえたはずの</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">44,000</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">円」だけ。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">◆ M</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">列（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">10%OFF</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">の値引額）と </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">I</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">列（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">44,000</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">円）を比べると、モデレート以上の高額パッケージでは検査診断料無料のほうが医院の負担が小さい。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFC00000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">◆【要注意】ライト両顎</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFC00000"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(43,780)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFC00000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">・ライト片顎</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFC00000"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(39,380)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFC00000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">・エクスプレス両顎</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFC00000"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(32,780)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFC00000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">・エクスプレス片顎</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFC00000"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(29,800)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFC00000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">は、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFC00000"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">10%OFF</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFC00000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">のほうが</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFC00000"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">44,000</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFC00000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">円より安く済む（フェーズ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFC00000"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFC00000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">は</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFC00000"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">44,000</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFC00000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">円で同額）。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFC00000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">　　ただし表を</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFC00000"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFC00000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">本立てにすると現場が混乱し「じゃあ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFC00000"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">10%OFF</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFC00000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">で」と言われる口実にもなるため、全パッケージ一律「検査診断料無料」で統一する。差額は最大</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFC00000"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">14,200</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFC00000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">円（エクスプレス片顎）。</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">運用上の注意（元データより引き継ぎ）</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">◆ 原価合計＝パッケージ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(22%OFF</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">後</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">＋手数料</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3,400</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（初回アライナー＋ビベラの</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">回分）＋ビベラ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">セット（定価・割引対象外）。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">◆ 追加アライナーが出るたびに手数料</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+1,700</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">円、コンプリ オプション</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">・モデレート・ライト・フェーズ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">は追加</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">回ごとに本体費用も発生する（元データ参照）。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">◆ エクスプレスはアラインの割引が一切効かない（片顎</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">78,000</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">／両顎</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">100,000</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">が丸ごと請求）。粗利率が最も低いので、紹介プランでも値引きはしない。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">◆ iTero</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">送信の症例はキャンセル料</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">円（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">PVS</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">印象は</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">30,000</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">円）。ロイ様紹介の症例は必ず</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">iTero</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">で提出する運用にすると、キャンセル時の損失をゼロにできる。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFC00000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">◆ ロイ様から矯正の値引きを強く求められた場合の最終ラインは</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFC00000"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">M</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFC00000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">列（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFC00000"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">10%OFF</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFC00000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）。ただし院長判断とし、価格表には載せない。</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">従来の「月額紹介料」と、新方式「紹介の方への値引き」の損益比較</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF666666"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">この制度の最大のメリットは、紹介料が固定費から変動費に変わること。紹介がゼロの月の医院負担は、従来＝月額まるごと／新方式＝</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF666666"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF666666"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">円。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF666666"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">単位：円。補綴の「通常割引率」は既存の本数ルール（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF666666"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF666666"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">〜</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF666666"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF666666"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">本</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF666666"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">10%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF666666"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">／</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF666666"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">6</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF666666"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">〜</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF666666"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">9</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF666666"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">本</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF666666"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">15%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF666666"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">／</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF666666"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">10</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF666666"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">本以上</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF666666"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">20%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF666666"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）を自動適用。矯正は原則値引きなしのため通常割引率</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF666666"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">0%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF666666"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">。</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">【設定値】従来ロイ様に毎月お支払いしていた紹介料の実額を入れてください（青字＝入力セル）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">従来の月額紹介料（実額に置き換えてください）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">円／月　★仮の数値です。必ず実額に修正してください</t>
-  </si>
-  <si>
-    <t xml:space="preserve">従来方式の年間負担</t>
-  </si>
-  <si>
-    <t xml:space="preserve">円／年（紹介人数がゼロでも発生）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">想定ケース</t>
-  </si>
-  <si>
-    <t xml:space="preserve">本数／件数</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">単価</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">定価</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">定価合計</t>
-  </si>
-  <si>
-    <t xml:space="preserve">通常の
-割引率</t>
-  </si>
-  <si>
-    <t xml:space="preserve">紹介がなくても
-出していた価格</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ロイ紹介価格</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">患者メリット
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
       <t xml:space="preserve">定価との差</t>
     </r>
     <r>
@@ -3768,7 +3696,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">■ 矯正（インビザライン）｜ロイ紹介＝定価据え置き＋矯正検査診断料 </t>
+      <t xml:space="preserve">■ 矯正（インビザライン）｜ロイ紹介＝①矯正治療費は据え置き、②矯正検査診断料 </t>
     </r>
     <r>
       <rPr>
@@ -3787,7 +3715,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">円 無料</t>
+      <t xml:space="preserve">円のみ無料</t>
     </r>
   </si>
   <si>
@@ -4244,7 +4172,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">◆ 矯正はもともと値引きゼロのため、実質負担＝</t>
+      <t xml:space="preserve">◆ 矯正の治療費は据え置きなので値引きゼロ。実質負担＝別建て請求の検査診断料</t>
     </r>
     <r>
       <rPr>
@@ -4261,7 +4189,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">円（本来もらえたはずの検査診断料）が</t>
+      <t xml:space="preserve">円（本来もらえたはずの分）が</t>
     </r>
     <r>
       <rPr>
@@ -4278,7 +4206,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">件ごとにそのまま発生する。</t>
+      <t xml:space="preserve">件ごとに発生する。</t>
     </r>
   </si>
   <si>
@@ -4764,7 +4692,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">◆ 矯正（インビザライン）：パッケージは定価据え置き。そのかわり矯正検査診断料 </t>
+      <t xml:space="preserve">◆ 矯正（インビザライン）：請求は【①矯正治療費】と【②矯正検査診断料 </t>
     </r>
     <r>
       <rPr>
@@ -4781,7 +4709,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">円（税込）を無料。</t>
+      <t xml:space="preserve">円】の別建て。①は定価据え置きのまま、②のみを無料にする。</t>
     </r>
   </si>
   <si>
@@ -5406,6 +5334,19 @@
     </font>
     <font>
       <b val="true"/>
+      <sz val="10"/>
+      <name val="WenQuanYi Zen Hei"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <name val="游ゴシック"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
       <sz val="12"/>
       <color rgb="FF0000FF"/>
       <name val="游ゴシック"/>
@@ -5424,19 +5365,6 @@
       <color rgb="FF666666"/>
       <name val="WenQuanYi Zen Hei"/>
       <family val="2"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="10"/>
-      <name val="WenQuanYi Zen Hei"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="10"/>
-      <name val="游ゴシック"/>
-      <family val="0"/>
-      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -5638,6 +5566,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -5646,11 +5578,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="21" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="23" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5658,7 +5590,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5667,10 +5599,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="13" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -6599,7 +6527,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M38"/>
+  <dimension ref="A1:M39"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="42"/>
@@ -7497,21 +7425,21 @@
       <c r="M33" s="17"/>
     </row>
     <row r="34" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="20" t="s">
+      <c r="A34" s="23" t="s">
         <v>82</v>
       </c>
-      <c r="B34" s="20"/>
-      <c r="C34" s="20"/>
-      <c r="D34" s="20"/>
-      <c r="E34" s="20"/>
-      <c r="F34" s="20"/>
-      <c r="G34" s="20"/>
-      <c r="H34" s="20"/>
-      <c r="I34" s="20"/>
-      <c r="J34" s="20"/>
-      <c r="K34" s="20"/>
-      <c r="L34" s="20"/>
-      <c r="M34" s="20"/>
+      <c r="B34" s="23"/>
+      <c r="C34" s="23"/>
+      <c r="D34" s="23"/>
+      <c r="E34" s="23"/>
+      <c r="F34" s="23"/>
+      <c r="G34" s="23"/>
+      <c r="H34" s="23"/>
+      <c r="I34" s="23"/>
+      <c r="J34" s="23"/>
+      <c r="K34" s="23"/>
+      <c r="L34" s="23"/>
+      <c r="M34" s="23"/>
     </row>
     <row r="35" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="20" t="s">
@@ -7548,41 +7476,58 @@
       <c r="M36" s="20"/>
     </row>
     <row r="37" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="18" t="s">
+      <c r="A37" s="20" t="s">
         <v>85</v>
       </c>
-      <c r="B37" s="18"/>
-      <c r="C37" s="18"/>
-      <c r="D37" s="18"/>
-      <c r="E37" s="18"/>
-      <c r="F37" s="18"/>
-      <c r="G37" s="18"/>
-      <c r="H37" s="18"/>
-      <c r="I37" s="18"/>
-      <c r="J37" s="18"/>
-      <c r="K37" s="18"/>
-      <c r="L37" s="18"/>
-      <c r="M37" s="18"/>
+      <c r="B37" s="20"/>
+      <c r="C37" s="20"/>
+      <c r="D37" s="20"/>
+      <c r="E37" s="20"/>
+      <c r="F37" s="20"/>
+      <c r="G37" s="20"/>
+      <c r="H37" s="20"/>
+      <c r="I37" s="20"/>
+      <c r="J37" s="20"/>
+      <c r="K37" s="20"/>
+      <c r="L37" s="20"/>
+      <c r="M37" s="20"/>
     </row>
     <row r="38" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="19" t="s">
+      <c r="A38" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="B38" s="19"/>
-      <c r="C38" s="19"/>
-      <c r="D38" s="19"/>
-      <c r="E38" s="19"/>
-      <c r="F38" s="19"/>
-      <c r="G38" s="19"/>
-      <c r="H38" s="19"/>
-      <c r="I38" s="19"/>
-      <c r="J38" s="19"/>
-      <c r="K38" s="19"/>
-      <c r="L38" s="19"/>
-      <c r="M38" s="19"/>
+      <c r="B38" s="18"/>
+      <c r="C38" s="18"/>
+      <c r="D38" s="18"/>
+      <c r="E38" s="18"/>
+      <c r="F38" s="18"/>
+      <c r="G38" s="18"/>
+      <c r="H38" s="18"/>
+      <c r="I38" s="18"/>
+      <c r="J38" s="18"/>
+      <c r="K38" s="18"/>
+      <c r="L38" s="18"/>
+      <c r="M38" s="18"/>
+    </row>
+    <row r="39" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="B39" s="19"/>
+      <c r="C39" s="19"/>
+      <c r="D39" s="19"/>
+      <c r="E39" s="19"/>
+      <c r="F39" s="19"/>
+      <c r="G39" s="19"/>
+      <c r="H39" s="19"/>
+      <c r="I39" s="19"/>
+      <c r="J39" s="19"/>
+      <c r="K39" s="19"/>
+      <c r="L39" s="19"/>
+      <c r="M39" s="19"/>
     </row>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="20">
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="A2:M2"/>
     <mergeCell ref="A3:M3"/>
@@ -7602,6 +7547,7 @@
     <mergeCell ref="A36:M36"/>
     <mergeCell ref="A37:M37"/>
     <mergeCell ref="A38:M38"/>
+    <mergeCell ref="A39:M39"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -7635,7 +7581,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -7649,38 +7595,38 @@
       <c r="K1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="23" t="s">
-        <v>88</v>
-      </c>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="23"/>
-      <c r="F2" s="23"/>
-      <c r="G2" s="23"/>
-      <c r="H2" s="23"/>
-      <c r="I2" s="23"/>
-      <c r="J2" s="23"/>
-      <c r="K2" s="23"/>
+      <c r="A2" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+      <c r="H2" s="24"/>
+      <c r="I2" s="24"/>
+      <c r="J2" s="24"/>
+      <c r="K2" s="24"/>
     </row>
     <row r="3" customFormat="false" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="23" t="s">
-        <v>89</v>
-      </c>
-      <c r="B3" s="23"/>
-      <c r="C3" s="23"/>
-      <c r="D3" s="23"/>
-      <c r="E3" s="23"/>
-      <c r="F3" s="23"/>
-      <c r="G3" s="23"/>
-      <c r="H3" s="23"/>
-      <c r="I3" s="23"/>
-      <c r="J3" s="23"/>
-      <c r="K3" s="23"/>
+      <c r="A3" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="B3" s="24"/>
+      <c r="C3" s="24"/>
+      <c r="D3" s="24"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="24"/>
+      <c r="H3" s="24"/>
+      <c r="I3" s="24"/>
+      <c r="J3" s="24"/>
+      <c r="K3" s="24"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -7694,58 +7640,58 @@
       <c r="K5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="24" t="s">
-        <v>91</v>
-      </c>
-      <c r="D6" s="25" t="n">
+      <c r="A6" s="25" t="s">
+        <v>92</v>
+      </c>
+      <c r="D6" s="26" t="n">
         <v>50000</v>
       </c>
-      <c r="E6" s="26" t="s">
-        <v>92</v>
+      <c r="E6" s="27" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="D7" s="27" t="n">
+        <v>94</v>
+      </c>
+      <c r="D7" s="28" t="n">
         <f aca="false">D6*12</f>
         <v>600000</v>
       </c>
-      <c r="E7" s="28" t="s">
-        <v>94</v>
+      <c r="E7" s="29" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J9" s="8" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K9" s="8" t="s">
         <v>14</v>
@@ -7753,7 +7699,7 @@
     </row>
     <row r="10" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B10" s="9"/>
       <c r="C10" s="9"/>
@@ -7768,7 +7714,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B11" s="10" t="n">
         <v>1</v>
@@ -7789,7 +7735,7 @@
         <f aca="false">ROUND(C11*(1-E11),0)*B11</f>
         <v>89100</v>
       </c>
-      <c r="G11" s="29" t="n">
+      <c r="G11" s="30" t="n">
         <f aca="false">ロイ紹介_補綴価格表!D11*B11</f>
         <v>79200</v>
       </c>
@@ -7797,7 +7743,7 @@
         <f aca="false">D11-G11</f>
         <v>19800</v>
       </c>
-      <c r="I11" s="30" t="n">
+      <c r="I11" s="31" t="n">
         <f aca="false">F11-G11</f>
         <v>9900</v>
       </c>
@@ -7812,7 +7758,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B12" s="10" t="n">
         <v>3</v>
@@ -7833,7 +7779,7 @@
         <f aca="false">ROUND(C12*(1-E12),0)*B12</f>
         <v>267300</v>
       </c>
-      <c r="G12" s="29" t="n">
+      <c r="G12" s="30" t="n">
         <f aca="false">ロイ紹介_補綴価格表!D11*B12</f>
         <v>237600</v>
       </c>
@@ -7841,7 +7787,7 @@
         <f aca="false">D12-G12</f>
         <v>59400</v>
       </c>
-      <c r="I12" s="30" t="n">
+      <c r="I12" s="31" t="n">
         <f aca="false">F12-G12</f>
         <v>29700</v>
       </c>
@@ -7856,7 +7802,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B13" s="10" t="n">
         <v>2</v>
@@ -7877,7 +7823,7 @@
         <f aca="false">ROUND(C13*(1-E13),0)*B13</f>
         <v>99000</v>
       </c>
-      <c r="G13" s="29" t="n">
+      <c r="G13" s="30" t="n">
         <f aca="false">ロイ紹介_補綴価格表!D13*B13</f>
         <v>88000</v>
       </c>
@@ -7885,7 +7831,7 @@
         <f aca="false">D13-G13</f>
         <v>22000</v>
       </c>
-      <c r="I13" s="30" t="n">
+      <c r="I13" s="31" t="n">
         <f aca="false">F13-G13</f>
         <v>11000</v>
       </c>
@@ -7900,7 +7846,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B14" s="10" t="n">
         <v>4</v>
@@ -7921,7 +7867,7 @@
         <f aca="false">ROUND(C14*(1-E14),0)*B14</f>
         <v>514800</v>
       </c>
-      <c r="G14" s="29" t="n">
+      <c r="G14" s="30" t="n">
         <f aca="false">ロイ紹介_補綴価格表!D16*B14</f>
         <v>457600</v>
       </c>
@@ -7929,7 +7875,7 @@
         <f aca="false">D14-G14</f>
         <v>114400</v>
       </c>
-      <c r="I14" s="30" t="n">
+      <c r="I14" s="31" t="n">
         <f aca="false">F14-G14</f>
         <v>57200</v>
       </c>
@@ -7944,7 +7890,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B15" s="10" t="n">
         <v>6</v>
@@ -7965,7 +7911,7 @@
         <f aca="false">ROUND(C15*(1-E15),0)*B15</f>
         <v>729300</v>
       </c>
-      <c r="G15" s="29" t="n">
+      <c r="G15" s="30" t="n">
         <f aca="false">ロイ紹介_補綴価格表!D16*B15</f>
         <v>686400</v>
       </c>
@@ -7973,7 +7919,7 @@
         <f aca="false">D15-G15</f>
         <v>171600</v>
       </c>
-      <c r="I15" s="30" t="n">
+      <c r="I15" s="31" t="n">
         <f aca="false">F15-G15</f>
         <v>42900</v>
       </c>
@@ -7988,7 +7934,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B16" s="10" t="n">
         <v>6</v>
@@ -8009,7 +7955,7 @@
         <f aca="false">ROUND(C16*(1-E16),0)*B16</f>
         <v>504900</v>
       </c>
-      <c r="G16" s="29" t="n">
+      <c r="G16" s="30" t="n">
         <f aca="false">ロイ紹介_補綴価格表!D19*B16</f>
         <v>475200</v>
       </c>
@@ -8017,7 +7963,7 @@
         <f aca="false">D16-G16</f>
         <v>118800</v>
       </c>
-      <c r="I16" s="30" t="n">
+      <c r="I16" s="31" t="n">
         <f aca="false">F16-G16</f>
         <v>29700</v>
       </c>
@@ -8032,7 +7978,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B17" s="10" t="n">
         <v>6</v>
@@ -8053,7 +7999,7 @@
         <f aca="false">ROUND(C17*(1-E17),0)*B17</f>
         <v>561000</v>
       </c>
-      <c r="G17" s="29" t="n">
+      <c r="G17" s="30" t="n">
         <f aca="false">ロイ紹介_補綴価格表!D18*B17</f>
         <v>528000</v>
       </c>
@@ -8061,7 +8007,7 @@
         <f aca="false">D17-G17</f>
         <v>132000</v>
       </c>
-      <c r="I17" s="30" t="n">
+      <c r="I17" s="31" t="n">
         <f aca="false">F17-G17</f>
         <v>33000</v>
       </c>
@@ -8076,7 +8022,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B18" s="10" t="n">
         <v>12</v>
@@ -8097,7 +8043,7 @@
         <f aca="false">ROUND(C18*(1-E18),0)*B18</f>
         <v>1056000</v>
       </c>
-      <c r="G18" s="29" t="n">
+      <c r="G18" s="30" t="n">
         <f aca="false">ロイ紹介_補綴価格表!D17*B18</f>
         <v>1056000</v>
       </c>
@@ -8105,7 +8051,7 @@
         <f aca="false">D18-G18</f>
         <v>264000</v>
       </c>
-      <c r="I18" s="30" t="n">
+      <c r="I18" s="31" t="n">
         <f aca="false">F18-G18</f>
         <v>0</v>
       </c>
@@ -8120,7 +8066,7 @@
     </row>
     <row r="20" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B20" s="9"/>
       <c r="C20" s="9"/>
@@ -8135,7 +8081,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B21" s="10" t="n">
         <v>1</v>
@@ -8155,7 +8101,7 @@
         <f aca="false">D21</f>
         <v>924000</v>
       </c>
-      <c r="G21" s="29" t="n">
+      <c r="G21" s="30" t="n">
         <f aca="false">ロイ紹介_矯正価格表!H12*B21</f>
         <v>880000</v>
       </c>
@@ -8163,7 +8109,7 @@
         <f aca="false">D21-G21</f>
         <v>44000</v>
       </c>
-      <c r="I21" s="30" t="n">
+      <c r="I21" s="31" t="n">
         <f aca="false">F21-G21</f>
         <v>44000</v>
       </c>
@@ -8178,7 +8124,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B22" s="10" t="n">
         <v>1</v>
@@ -8198,7 +8144,7 @@
         <f aca="false">D22</f>
         <v>591800</v>
       </c>
-      <c r="G22" s="29" t="n">
+      <c r="G22" s="30" t="n">
         <f aca="false">ロイ紹介_矯正価格表!H13*B22</f>
         <v>547800</v>
       </c>
@@ -8206,7 +8152,7 @@
         <f aca="false">D22-G22</f>
         <v>44000</v>
       </c>
-      <c r="I22" s="30" t="n">
+      <c r="I22" s="31" t="n">
         <f aca="false">F22-G22</f>
         <v>44000</v>
       </c>
@@ -8221,7 +8167,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B23" s="10" t="n">
         <v>1</v>
@@ -8241,7 +8187,7 @@
         <f aca="false">D23</f>
         <v>481800</v>
       </c>
-      <c r="G23" s="29" t="n">
+      <c r="G23" s="30" t="n">
         <f aca="false">ロイ紹介_矯正価格表!H15*B23</f>
         <v>437800</v>
       </c>
@@ -8249,7 +8195,7 @@
         <f aca="false">D23-G23</f>
         <v>44000</v>
       </c>
-      <c r="I23" s="30" t="n">
+      <c r="I23" s="31" t="n">
         <f aca="false">F23-G23</f>
         <v>44000</v>
       </c>
@@ -8264,7 +8210,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B24" s="10" t="n">
         <v>1</v>
@@ -8284,7 +8230,7 @@
         <f aca="false">D24</f>
         <v>594000</v>
       </c>
-      <c r="G24" s="29" t="n">
+      <c r="G24" s="30" t="n">
         <f aca="false">ロイ紹介_矯正価格表!H21*B24</f>
         <v>550000</v>
       </c>
@@ -8292,7 +8238,7 @@
         <f aca="false">D24-G24</f>
         <v>44000</v>
       </c>
-      <c r="I24" s="30" t="n">
+      <c r="I24" s="31" t="n">
         <f aca="false">F24-G24</f>
         <v>44000</v>
       </c>
@@ -8307,7 +8253,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B25" s="10" t="n">
         <v>1</v>
@@ -8327,7 +8273,7 @@
         <f aca="false">D25</f>
         <v>484000</v>
       </c>
-      <c r="G25" s="29" t="n">
+      <c r="G25" s="30" t="n">
         <f aca="false">ロイ紹介_矯正価格表!H24*B25</f>
         <v>440000</v>
       </c>
@@ -8335,7 +8281,7 @@
         <f aca="false">D25-G25</f>
         <v>44000</v>
       </c>
-      <c r="I25" s="30" t="n">
+      <c r="I25" s="31" t="n">
         <f aca="false">F25-G25</f>
         <v>44000</v>
       </c>
@@ -8350,7 +8296,7 @@
     </row>
     <row r="27" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="17" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B27" s="17"/>
       <c r="C27" s="17"/>
@@ -8365,7 +8311,7 @@
     </row>
     <row r="28" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="18" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B28" s="18"/>
       <c r="C28" s="18"/>
@@ -8379,23 +8325,23 @@
       <c r="K28" s="18"/>
     </row>
     <row r="29" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="31" t="s">
-        <v>122</v>
-      </c>
-      <c r="B29" s="31"/>
-      <c r="C29" s="31"/>
-      <c r="D29" s="31"/>
-      <c r="E29" s="31"/>
-      <c r="F29" s="31"/>
-      <c r="G29" s="31"/>
-      <c r="H29" s="31"/>
-      <c r="I29" s="31"/>
-      <c r="J29" s="31"/>
-      <c r="K29" s="31"/>
+      <c r="A29" s="23" t="s">
+        <v>123</v>
+      </c>
+      <c r="B29" s="23"/>
+      <c r="C29" s="23"/>
+      <c r="D29" s="23"/>
+      <c r="E29" s="23"/>
+      <c r="F29" s="23"/>
+      <c r="G29" s="23"/>
+      <c r="H29" s="23"/>
+      <c r="I29" s="23"/>
+      <c r="J29" s="23"/>
+      <c r="K29" s="23"/>
     </row>
     <row r="30" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="20" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B30" s="20"/>
       <c r="C30" s="20"/>
@@ -8410,7 +8356,7 @@
     </row>
     <row r="31" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="20" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B31" s="20"/>
       <c r="C31" s="20"/>
@@ -8425,7 +8371,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
@@ -8440,28 +8386,28 @@
     </row>
     <row r="35" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B35" s="32" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E35" s="8" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H35" s="8" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I35" s="8"/>
       <c r="J35" s="8"/>
@@ -8469,9 +8415,9 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="B36" s="27" t="n">
+        <v>107</v>
+      </c>
+      <c r="B36" s="28" t="n">
         <f aca="false">I11</f>
         <v>9900</v>
       </c>
@@ -8502,9 +8448,9 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="B37" s="27" t="n">
+        <v>108</v>
+      </c>
+      <c r="B37" s="28" t="n">
         <f aca="false">I12</f>
         <v>29700</v>
       </c>
@@ -8535,9 +8481,9 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="B38" s="27" t="n">
+        <v>111</v>
+      </c>
+      <c r="B38" s="28" t="n">
         <f aca="false">I15</f>
         <v>42900</v>
       </c>
@@ -8568,9 +8514,9 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="B39" s="27" t="n">
+        <v>114</v>
+      </c>
+      <c r="B39" s="28" t="n">
         <f aca="false">I18</f>
         <v>0</v>
       </c>
@@ -8601,9 +8547,9 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="B40" s="27" t="n">
+        <v>117</v>
+      </c>
+      <c r="B40" s="28" t="n">
         <f aca="false">I22</f>
         <v>44000</v>
       </c>
@@ -8633,23 +8579,23 @@
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="23" t="s">
-        <v>133</v>
-      </c>
-      <c r="B41" s="23"/>
-      <c r="C41" s="23"/>
-      <c r="D41" s="23"/>
-      <c r="E41" s="23"/>
-      <c r="F41" s="23"/>
-      <c r="G41" s="23"/>
-      <c r="H41" s="23"/>
-      <c r="I41" s="23"/>
-      <c r="J41" s="23"/>
-      <c r="K41" s="23"/>
+      <c r="A41" s="24" t="s">
+        <v>134</v>
+      </c>
+      <c r="B41" s="24"/>
+      <c r="C41" s="24"/>
+      <c r="D41" s="24"/>
+      <c r="E41" s="24"/>
+      <c r="F41" s="24"/>
+      <c r="G41" s="24"/>
+      <c r="H41" s="24"/>
+      <c r="I41" s="24"/>
+      <c r="J41" s="24"/>
+      <c r="K41" s="24"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="17" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B43" s="17"/>
       <c r="C43" s="17"/>
@@ -8664,7 +8610,7 @@
     </row>
     <row r="44" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="20" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B44" s="20"/>
       <c r="C44" s="20"/>
@@ -8678,23 +8624,23 @@
       <c r="K44" s="20"/>
     </row>
     <row r="45" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="31" t="s">
-        <v>136</v>
-      </c>
-      <c r="B45" s="31"/>
-      <c r="C45" s="31"/>
-      <c r="D45" s="31"/>
-      <c r="E45" s="31"/>
-      <c r="F45" s="31"/>
-      <c r="G45" s="31"/>
-      <c r="H45" s="31"/>
-      <c r="I45" s="31"/>
-      <c r="J45" s="31"/>
-      <c r="K45" s="31"/>
+      <c r="A45" s="23" t="s">
+        <v>137</v>
+      </c>
+      <c r="B45" s="23"/>
+      <c r="C45" s="23"/>
+      <c r="D45" s="23"/>
+      <c r="E45" s="23"/>
+      <c r="F45" s="23"/>
+      <c r="G45" s="23"/>
+      <c r="H45" s="23"/>
+      <c r="I45" s="23"/>
+      <c r="J45" s="23"/>
+      <c r="K45" s="23"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="19" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B46" s="19"/>
       <c r="C46" s="19"/>
@@ -8751,172 +8697,172 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="35" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="36" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="37" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="36" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="36" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="36" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="36" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="36" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="36" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="37" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
   </sheetData>

--- a/docs/referral-pricing/ロイ様ご紹介プラン_価格表.xlsx
+++ b/docs/referral-pricing/ロイ様ご紹介プラン_価格表.xlsx
@@ -4534,16 +4534,114 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">◆ 対象＝ロイ様が代表を務めるお店の在籍スタッフ本人。初診の受付時に「ロイさんの紹介」と申告があった方に限る。</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">◆ 同伴者への適用範囲（本人のみ／同伴</t>
+    <t xml:space="preserve">◆ 対象＝ロイ様からのご紹介であれば誰でも。お店の在籍スタッフに限定しない（院長決裁事項）。初診の受付時に「ロイさんの紹介」と申告があった方。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">◆ 【重要】対象を「ロイ様の紹介」とする以上、店舗の在籍者に限定した場合より範囲は広い。紹介の連鎖も起こりうるため、月間上限と有効期限を必ずセットで決める。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">◆ 【重要】自費診療のみが対象。保険診療の一部負担金は法令上、値引き・免除ができないため必ず対象外とする。</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">◆ 他の割引・キャンペーン・モニター価格との併用は不可。本数によるまとめ割引とも併用しない（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">20%OFF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">が上限で、それ以上は重ねない）。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">◆ 補綴</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">20%OFF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">は当院の値引き下限。「もう少し」と言われても、これ以上は下げられない旨を最初に伝えておく。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2. </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">価格の中身</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">◆ 補綴（セラミック治療）：全品目 一律</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">20%OFF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">。</t>
     </r>
     <r>
       <rPr>
@@ -4560,65 +4658,82 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">名まで／お店の関係者全般）は、ロイ様と事前に文書で合意しておく。ここを曖昧にすると際限なく広がる。</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">◆ 【重要】自費診療のみが対象。保険診療の一部負担金は法令上、値引き・免除ができないため必ず対象外とする。</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">◆ 他の割引・キャンペーン・モニター価格との併用は不可。本数によるまとめ割引とも併用しない（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">20%OFF</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">が上限で、それ以上は重ねない）。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">◆ 補綴</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">20%OFF</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">は当院の値引き下限。「もう少し」と言われても、これ以上は下げられない旨を最初に伝えておく。</t>
-    </r>
+      <t xml:space="preserve">本から適用、本数の条件なし。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">◆ 矯正（インビザライン）：請求は【①矯正治療費】と【②矯正検査診断料 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">44,000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">円】の別建て。①は定価据え置きのまま、②のみを無料にする。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">◆ 矯正のパッケージ価格を下げないのは、粗利率が</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">64</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">76%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">と低く値引きの余地がないため。検査診断料は原価ゼロなので、同じ「お得感」を医院の持ち出しゼロで出せる。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">◆ ホワイトニング・インプラント等は元データに粗利情報が無いため本表に含めていない。追加したい場合は原価がわかり次第、同じ形式で追記する。</t>
   </si>
   <si>
     <r>
@@ -4629,7 +4744,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">2. </t>
+      <t xml:space="preserve">3. </t>
     </r>
     <r>
       <rPr>
@@ -4638,126 +4753,65 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">価格の中身</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">◆ 補綴（セラミック治療）：全品目 一律</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">20%OFF</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">本から適用、本数の条件なし。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">◆ 矯正（インビザライン）：請求は【①矯正治療費】と【②矯正検査診断料 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">44,000</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">円】の別建て。①は定価据え置きのまま、②のみを無料にする。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">◆ 矯正のパッケージ価格を下げないのは、粗利率が</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">64</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">〜</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">76%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">と低く値引きの余地がないため。検査診断料は原価ゼロなので、同じ「お得感」を医院の持ち出しゼロで出せる。</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">◆ ホワイトニング・インプラント等は元データに粗利情報が無いため本表に含めていない。追加したい場合は原価がわかり次第、同じ形式で追記する。</t>
+      <t xml:space="preserve">上限と期限（必ず決めておく）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">◆ 月間の値引き総額に上限を設ける（例：月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">万円分まで）。上限に達した場合は翌月に繰り越し、という運用にすると医院側の読みが立つ。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">◆ 有効期限を切る（例：初回は</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">か月間、以降は実績を見て更新）。無期限にすると、紹介が止まっても価格だけが残り続ける。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">◆ 更新の判断材料として、月ごとの「紹介来院数／売上／値引き総額」を必ず記録する。従来の月額紹介料と比べて安いか高いかを毎月見る。</t>
   </si>
   <si>
     <r>
@@ -4768,7 +4822,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">3. </t>
+      <t xml:space="preserve">4. </t>
     </r>
     <r>
       <rPr>
@@ -4777,65 +4831,55 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">上限と期限（必ず決めておく）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">◆ 月間の値引き総額に上限を設ける（例：月</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">20</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">万円分まで）。上限に達した場合は翌月に繰り越し、という運用にすると医院側の読みが立つ。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">◆ 有効期限を切る（例：初回は</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">6</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">か月間、以降は実績を見て更新）。無期限にすると、紹介が止まっても価格だけが残り続ける。</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">◆ 更新の判断材料として、月ごとの「紹介来院数／売上／値引き総額」を必ず記録する。従来の月額紹介料と比べて安いか高いかを毎月見る。</t>
+      <t xml:space="preserve">紹介の確認方法</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">◆ 紹介カード（ロイ様のお店の名前入り）を渡す、またはロイ様からの</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">LINE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">DM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">のスクリーンショット提示を条件にする。口頭申告だけだと後から検証できない。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">◆ カルテまたは予約システムに「ロイ様紹介」のタグを付け、集計できるようにする。</t>
   </si>
   <si>
     <r>
@@ -4846,7 +4890,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">4. </t>
+      <t xml:space="preserve">5. </t>
     </r>
     <r>
       <rPr>
@@ -4855,79 +4899,11 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">紹介の確認方法</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">◆ 紹介カード（ロイ様のお店の名前入り）を渡す、またはロイ様からの</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">LINE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">・</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">DM</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">のスクリーンショット提示を条件にする。口頭申告だけだと後から検証できない。</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">◆ カルテまたは予約システムに「ロイ様紹介」のタグを付け、集計できるようにする。</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">5. </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
       <t xml:space="preserve">ロイ様への説明のしかた（ここが交渉のポイント）</t>
     </r>
   </si>
   <si>
-    <t xml:space="preserve">◆ 「紹介料をやめる」ではなく「紹介料を、スタッフさんが直接受け取れる形に変える」という説明にする。ロイ様のお店から見れば福利厚生になる。</t>
+    <t xml:space="preserve">◆ 「紹介料をやめる」ではなく「紹介料を、ご紹介した方が直接受け取れる形に変える」という説明にする。ロイ様から見れば人に勧めやすい材料になる。</t>
   </si>
   <si>
     <r>
@@ -8715,8 +8691,8 @@
         <v>142</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="37" t="s">
         <v>143</v>
       </c>
     </row>
